--- a/КЦТ_1.xlsx
+++ b/КЦТ_1.xlsx
@@ -465,37 +465,37 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Side1</t>
+          <t>Side1_tdif</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Side2</t>
+          <t>Side2_tdif</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Side3</t>
+          <t>Side3_tdif</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>k_sch_1</t>
+          <t>ksch1_tdif</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>k_sch_2</t>
+          <t>ksch2_tdif</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>compens_3i0_vn</t>
+          <t>comp3i0_rmxu1_tdif</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>compens_3i0_nn</t>
+          <t>comp3i0_rmxu2_tdif</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -797,57 +797,57 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Sbaz</t>
+          <t>Sbaz_tdif</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Ubaz_vn</t>
+          <t>Ubaz_rmxu1_tdif</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Ubaz_nn</t>
+          <t>Ubaz_rmxu2_tdif</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Iperv_vn</t>
+          <t>Iperv_rmxu1_tdif</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Iperv_nn</t>
+          <t>Iperv_rmxu2_tdif</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Inom_term_vn</t>
+          <t>Inomterm_rmxu1_tdif</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Inom_term_nn</t>
+          <t>Inomterm_rmxu2_tdif</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Ivtor_vn</t>
+          <t>Ivtor_rmxu1_tdif</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Ivtor_nn</t>
+          <t>Ivtor_rmxu2_tdif</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>n_sch_vn</t>
+          <t>Nsch_rmxu1_tdif</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>n_sch_nn</t>
+          <t>Nsch_rmxu2_tdif</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
